--- a/supply_order_forms/032_team_celebration_party_supply_order_form--supply_order_forms.xlsx
+++ b/supply_order_forms/032_team_celebration_party_supply_order_form--supply_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -904,27 +904,10 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>donuts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Chips</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>party_supply_selections_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>donuts</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>Donuts</t>
         </is>
